--- a/PRD/海克斯版本.xlsx
+++ b/PRD/海克斯版本.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\panda_kang\Desktop\2026ballgame\PRD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13117\Desktop\2026\2026ballgame\PRD\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
